--- a/Misc Stuff/Library Research/ADCs/AXX131X0X/Register Maps.xlsx
+++ b/Misc Stuff/Library Research/ADCs/AXX131X0X/Register Maps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\Misc Stuff\Library Research\ADCs\AXX131X0X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EA61F2-89C5-40AB-9685-9CF282CEE13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0465384-5F99-4822-B5BA-E6237AB23986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7725" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="7725" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADS131M02" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="282">
   <si>
     <t>CRC_TYPE</t>
   </si>
@@ -891,9 +891,6 @@
   <si>
     <t>0x6</t>
   </si>
-  <si>
-    <t>NOTE: START BITS ARE SCREWED UP ON THIS SHEET!</t>
-  </si>
 </sst>
 </file>
 
@@ -921,18 +918,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -971,13 +962,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="30">
     <dxf>
       <fill>
         <patternFill>
@@ -996,34 +987,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1156,7 +1119,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1184,14 +1147,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1540,7 +1496,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="4"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -5504,17 +5460,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I2:I111">
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J111">
-    <cfRule type="cellIs" dxfId="33" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L111">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="notEqual">
       <formula>F2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5532,7 +5488,7 @@
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.08984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="45.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="45.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -5566,9 +5522,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -5584,7 +5538,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -5619,7 +5573,7 @@
         <v>253</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -5655,7 +5609,7 @@
         <v>80</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -5691,7 +5645,7 @@
         <v>88</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -5727,7 +5681,7 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5763,7 +5717,7 @@
         <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -5799,7 +5753,7 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5835,7 +5789,7 @@
         <v>88</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -5871,7 +5825,7 @@
         <v>89</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -5907,7 +5861,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -5943,7 +5897,7 @@
         <v>255</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -5979,7 +5933,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -6015,7 +5969,7 @@
         <v>88</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -6051,7 +6005,7 @@
         <v>88</v>
       </c>
       <c r="E15" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -6087,7 +6041,7 @@
         <v>91</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -6123,7 +6077,7 @@
         <v>88</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -6159,7 +6113,7 @@
         <v>88</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -6195,7 +6149,7 @@
         <v>88</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -6231,7 +6185,7 @@
         <v>89</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -6267,7 +6221,7 @@
         <v>90</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>2</v>
@@ -6303,7 +6257,7 @@
         <v>110</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -6339,7 +6293,7 @@
         <v>89</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -6375,7 +6329,7 @@
         <v>91</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>2</v>
@@ -6411,7 +6365,7 @@
         <v>88</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -6447,7 +6401,7 @@
         <v>88</v>
       </c>
       <c r="E26" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1">
         <v>1</v>
@@ -6483,7 +6437,7 @@
         <v>255</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -6519,7 +6473,7 @@
         <v>89</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -6555,7 +6509,7 @@
         <v>89</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -6591,7 +6545,7 @@
         <v>89</v>
       </c>
       <c r="E30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -6627,7 +6581,7 @@
         <v>110</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -6663,7 +6617,7 @@
         <v>114</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F32">
         <v>3</v>
@@ -6699,7 +6653,7 @@
         <v>116</v>
       </c>
       <c r="E33" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F33" s="1">
         <v>2</v>
@@ -6735,7 +6689,7 @@
         <v>255</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -6771,7 +6725,7 @@
         <v>110</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -6807,7 +6761,7 @@
         <v>88</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -6843,7 +6797,7 @@
         <v>110</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -6879,7 +6833,7 @@
         <v>88</v>
       </c>
       <c r="E38">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -6915,7 +6869,7 @@
         <v>110</v>
       </c>
       <c r="E39" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F39" s="1">
         <v>3</v>
@@ -6951,7 +6905,7 @@
         <v>246</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F40" s="2">
         <v>16</v>
@@ -6987,7 +6941,7 @@
         <v>110</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -7023,7 +6977,7 @@
         <v>132</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F42">
         <v>4</v>
@@ -7059,7 +7013,7 @@
         <v>88</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -7095,7 +7049,7 @@
         <v>88</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -7131,7 +7085,7 @@
         <v>110</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -7167,7 +7121,7 @@
         <v>110</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -7203,7 +7157,7 @@
         <v>88</v>
       </c>
       <c r="E47" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -7239,7 +7193,7 @@
         <v>136</v>
       </c>
       <c r="E48" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2">
         <v>16</v>
@@ -7275,7 +7229,7 @@
         <v>76</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F49">
         <v>8</v>
@@ -7311,7 +7265,7 @@
         <v>76</v>
       </c>
       <c r="E50" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="1">
         <v>8</v>
@@ -7347,7 +7301,7 @@
         <v>140</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F51">
         <v>10</v>
@@ -7383,7 +7337,7 @@
         <v>110</v>
       </c>
       <c r="E52">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52">
         <v>3</v>
@@ -7419,7 +7373,7 @@
         <v>88</v>
       </c>
       <c r="E53">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -7455,7 +7409,7 @@
         <v>91</v>
       </c>
       <c r="E54" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
@@ -7491,7 +7445,7 @@
         <v>136</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2">
         <v>16</v>
@@ -7527,7 +7481,7 @@
         <v>76</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F56">
         <v>8</v>
@@ -7563,7 +7517,7 @@
         <v>76</v>
       </c>
       <c r="E57" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F57" s="1">
         <v>8</v>
@@ -7599,7 +7553,7 @@
         <v>148</v>
       </c>
       <c r="E58" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F58" s="2">
         <v>16</v>
@@ -7635,7 +7589,7 @@
         <v>76</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F59">
         <v>8</v>
@@ -7671,7 +7625,7 @@
         <v>76</v>
       </c>
       <c r="E60" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F60" s="1">
         <v>8</v>
@@ -7707,7 +7661,7 @@
         <v>140</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F61">
         <v>10</v>
@@ -7743,7 +7697,7 @@
         <v>110</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -7779,7 +7733,7 @@
         <v>88</v>
       </c>
       <c r="E63">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -7815,7 +7769,7 @@
         <v>91</v>
       </c>
       <c r="E64" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F64" s="1">
         <v>2</v>
@@ -7851,7 +7805,7 @@
         <v>136</v>
       </c>
       <c r="E65" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2">
         <v>16</v>
@@ -7887,7 +7841,7 @@
         <v>76</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66">
         <v>8</v>
@@ -7923,7 +7877,7 @@
         <v>76</v>
       </c>
       <c r="E67" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1">
         <v>8</v>
@@ -7959,7 +7913,7 @@
         <v>148</v>
       </c>
       <c r="E68" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F68" s="2">
         <v>16</v>
@@ -7995,7 +7949,7 @@
         <v>76</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F69">
         <v>8</v>
@@ -8031,7 +7985,7 @@
         <v>76</v>
       </c>
       <c r="E70" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="1">
         <v>8</v>
@@ -8067,7 +8021,7 @@
         <v>140</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F71">
         <v>10</v>
@@ -8103,7 +8057,7 @@
         <v>110</v>
       </c>
       <c r="E72">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F72">
         <v>3</v>
@@ -8139,7 +8093,7 @@
         <v>88</v>
       </c>
       <c r="E73">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -8175,7 +8129,7 @@
         <v>91</v>
       </c>
       <c r="E74" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F74" s="1">
         <v>2</v>
@@ -8211,7 +8165,7 @@
         <v>136</v>
       </c>
       <c r="E75" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F75" s="2">
         <v>16</v>
@@ -8247,7 +8201,7 @@
         <v>76</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76">
         <v>8</v>
@@ -8283,7 +8237,7 @@
         <v>76</v>
       </c>
       <c r="E77" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" s="1">
         <v>8</v>
@@ -8319,7 +8273,7 @@
         <v>148</v>
       </c>
       <c r="E78" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F78" s="2">
         <v>16</v>
@@ -8355,7 +8309,7 @@
         <v>76</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79">
         <v>8</v>
@@ -8391,7 +8345,7 @@
         <v>76</v>
       </c>
       <c r="E80" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="1">
         <v>8</v>
@@ -8427,7 +8381,7 @@
         <v>246</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1">
         <v>16</v>
@@ -8463,7 +8417,7 @@
         <v>246</v>
       </c>
       <c r="E82" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2">
         <v>16</v>
@@ -8499,7 +8453,7 @@
         <v>246</v>
       </c>
       <c r="E83" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F83" s="2">
         <v>16</v>
@@ -8535,7 +8489,7 @@
         <v>246</v>
       </c>
       <c r="E84" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F84" s="2">
         <v>16</v>
@@ -8571,7 +8525,7 @@
         <v>246</v>
       </c>
       <c r="E85" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2">
         <v>16</v>
@@ -8607,7 +8561,7 @@
         <v>246</v>
       </c>
       <c r="E86" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2">
         <v>16</v>
@@ -8643,7 +8597,7 @@
         <v>246</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2">
         <v>16</v>
@@ -8679,7 +8633,7 @@
         <v>246</v>
       </c>
       <c r="E88" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F88" s="2">
         <v>16</v>
@@ -8715,7 +8669,7 @@
         <v>246</v>
       </c>
       <c r="E89" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2">
         <v>16</v>
@@ -8751,7 +8705,7 @@
         <v>246</v>
       </c>
       <c r="E90" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2">
         <v>16</v>
@@ -8787,7 +8741,7 @@
         <v>246</v>
       </c>
       <c r="E91" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1">
         <v>16</v>
@@ -8823,7 +8777,7 @@
         <v>246</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
@@ -8859,7 +8813,7 @@
         <v>246</v>
       </c>
       <c r="E93" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2">
         <v>16</v>
@@ -8895,7 +8849,7 @@
         <v>246</v>
       </c>
       <c r="E94" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F94" s="2">
         <v>16</v>
@@ -8931,7 +8885,7 @@
         <v>246</v>
       </c>
       <c r="E95" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2">
         <v>16</v>
@@ -8967,7 +8921,7 @@
         <v>246</v>
       </c>
       <c r="E96" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2">
         <v>16</v>
@@ -9003,7 +8957,7 @@
         <v>246</v>
       </c>
       <c r="E97" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2">
         <v>16</v>
@@ -9039,7 +8993,7 @@
         <v>246</v>
       </c>
       <c r="E98" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2">
         <v>16</v>
@@ -9075,7 +9029,7 @@
         <v>246</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F99" s="2">
         <v>16</v>
@@ -9111,7 +9065,7 @@
         <v>246</v>
       </c>
       <c r="E100" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2">
         <v>16</v>
@@ -9147,7 +9101,7 @@
         <v>246</v>
       </c>
       <c r="E101" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2">
         <v>16</v>
@@ -9183,7 +9137,7 @@
         <v>246</v>
       </c>
       <c r="E102" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
@@ -9219,7 +9173,7 @@
         <v>246</v>
       </c>
       <c r="E103" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2">
         <v>16</v>
@@ -9255,7 +9209,7 @@
         <v>246</v>
       </c>
       <c r="E104" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F104" s="2">
         <v>16</v>
@@ -9291,7 +9245,7 @@
         <v>246</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2">
         <v>16</v>
@@ -9327,7 +9281,7 @@
         <v>246</v>
       </c>
       <c r="E106" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1">
         <v>16</v>
@@ -9363,7 +9317,7 @@
         <v>246</v>
       </c>
       <c r="E107" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2">
         <v>16</v>
@@ -9399,7 +9353,7 @@
         <v>246</v>
       </c>
       <c r="E108" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2">
         <v>16</v>
@@ -9435,7 +9389,7 @@
         <v>246</v>
       </c>
       <c r="E109" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2">
         <v>16</v>
@@ -9471,7 +9425,7 @@
         <v>246</v>
       </c>
       <c r="E110" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F110" s="2">
         <v>16</v>
@@ -9507,7 +9461,7 @@
         <v>246</v>
       </c>
       <c r="E111" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F111" s="2">
         <v>16</v>
@@ -9543,7 +9497,7 @@
         <v>246</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2">
         <v>16</v>
@@ -9579,7 +9533,7 @@
         <v>246</v>
       </c>
       <c r="E113" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2">
         <v>16</v>
@@ -9615,7 +9569,7 @@
         <v>246</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F114" s="2">
         <v>16</v>
@@ -9651,7 +9605,7 @@
         <v>246</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2">
         <v>16</v>
@@ -9687,7 +9641,7 @@
         <v>246</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2">
         <v>16</v>
@@ -9723,7 +9677,7 @@
         <v>246</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2">
         <v>16</v>
@@ -9759,7 +9713,7 @@
         <v>246</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2">
         <v>16</v>
@@ -9795,7 +9749,7 @@
         <v>136</v>
       </c>
       <c r="E119" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F119" s="2">
         <v>16</v>
@@ -9831,7 +9785,7 @@
         <v>246</v>
       </c>
       <c r="E120" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F120" s="2">
         <v>16</v>
@@ -9855,23 +9809,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2 I121:I999">
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="26" priority="4" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I120">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="notEqual">
+      <formula>E3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J120">
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L120">
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I120">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9921,9 +9875,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -9939,7 +9891,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -9974,7 +9926,7 @@
         <v>256</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -10010,7 +9962,7 @@
         <v>80</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -10046,7 +9998,7 @@
         <v>88</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -10082,7 +10034,7 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -10118,7 +10070,7 @@
         <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -10154,7 +10106,7 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -10190,7 +10142,7 @@
         <v>88</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -10226,7 +10178,7 @@
         <v>89</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -10262,7 +10214,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -10298,7 +10250,7 @@
         <v>257</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -10334,7 +10286,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -10370,7 +10322,7 @@
         <v>88</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -10406,7 +10358,7 @@
         <v>88</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -10442,7 +10394,7 @@
         <v>88</v>
       </c>
       <c r="E16" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -10478,7 +10430,7 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -10514,7 +10466,7 @@
         <v>88</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -10550,7 +10502,7 @@
         <v>88</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -10586,7 +10538,7 @@
         <v>88</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -10622,7 +10574,7 @@
         <v>89</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -10658,7 +10610,7 @@
         <v>90</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -10694,7 +10646,7 @@
         <v>110</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -10730,7 +10682,7 @@
         <v>89</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -10766,7 +10718,7 @@
         <v>91</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -10802,7 +10754,7 @@
         <v>88</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -10838,7 +10790,7 @@
         <v>88</v>
       </c>
       <c r="E27" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
@@ -10874,7 +10826,7 @@
         <v>264</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -10910,7 +10862,7 @@
         <v>89</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -10946,7 +10898,7 @@
         <v>89</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -10982,7 +10934,7 @@
         <v>89</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -11018,7 +10970,7 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -11054,7 +11006,7 @@
         <v>110</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>3</v>
@@ -11090,7 +11042,7 @@
         <v>114</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -11126,7 +11078,7 @@
         <v>116</v>
       </c>
       <c r="E35" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F35" s="1">
         <v>2</v>
@@ -11162,7 +11114,7 @@
         <v>88</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -11198,7 +11150,7 @@
         <v>110</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F37">
         <v>3</v>
@@ -11234,7 +11186,7 @@
         <v>88</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -11270,7 +11222,7 @@
         <v>110</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -11306,7 +11258,7 @@
         <v>88</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -11342,7 +11294,7 @@
         <v>110</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -11378,7 +11330,7 @@
         <v>88</v>
       </c>
       <c r="E42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -11414,7 +11366,7 @@
         <v>110</v>
       </c>
       <c r="E43" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1">
         <v>3</v>
@@ -11450,7 +11402,7 @@
         <v>246</v>
       </c>
       <c r="E44" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
@@ -11486,7 +11438,7 @@
         <v>110</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -11522,7 +11474,7 @@
         <v>132</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F46">
         <v>4</v>
@@ -11558,7 +11510,7 @@
         <v>88</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -11594,7 +11546,7 @@
         <v>88</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -11630,7 +11582,7 @@
         <v>110</v>
       </c>
       <c r="E49">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F49">
         <v>3</v>
@@ -11666,7 +11618,7 @@
         <v>110</v>
       </c>
       <c r="E50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -11702,7 +11654,7 @@
         <v>88</v>
       </c>
       <c r="E51" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -11738,7 +11690,7 @@
         <v>136</v>
       </c>
       <c r="E52" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F52" s="2">
         <v>16</v>
@@ -11774,7 +11726,7 @@
         <v>76</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F53">
         <v>8</v>
@@ -11810,7 +11762,7 @@
         <v>76</v>
       </c>
       <c r="E54" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" s="1">
         <v>8</v>
@@ -11846,7 +11798,7 @@
         <v>140</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F55">
         <v>10</v>
@@ -11882,7 +11834,7 @@
         <v>110</v>
       </c>
       <c r="E56">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F56">
         <v>3</v>
@@ -11918,7 +11870,7 @@
         <v>88</v>
       </c>
       <c r="E57">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -11954,7 +11906,7 @@
         <v>91</v>
       </c>
       <c r="E58" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F58" s="1">
         <v>2</v>
@@ -11990,7 +11942,7 @@
         <v>136</v>
       </c>
       <c r="E59" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F59" s="2">
         <v>16</v>
@@ -12026,7 +11978,7 @@
         <v>76</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F60">
         <v>8</v>
@@ -12062,7 +12014,7 @@
         <v>76</v>
       </c>
       <c r="E61" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="1">
         <v>8</v>
@@ -12098,7 +12050,7 @@
         <v>148</v>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F62" s="2">
         <v>16</v>
@@ -12134,7 +12086,7 @@
         <v>76</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F63">
         <v>8</v>
@@ -12170,7 +12122,7 @@
         <v>76</v>
       </c>
       <c r="E64" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" s="1">
         <v>8</v>
@@ -12206,7 +12158,7 @@
         <v>140</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65">
         <v>10</v>
@@ -12242,7 +12194,7 @@
         <v>110</v>
       </c>
       <c r="E66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>3</v>
@@ -12278,7 +12230,7 @@
         <v>88</v>
       </c>
       <c r="E67">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -12314,7 +12266,7 @@
         <v>91</v>
       </c>
       <c r="E68" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F68" s="1">
         <v>2</v>
@@ -12350,7 +12302,7 @@
         <v>136</v>
       </c>
       <c r="E69" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F69" s="2">
         <v>16</v>
@@ -12386,7 +12338,7 @@
         <v>76</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F70">
         <v>8</v>
@@ -12422,7 +12374,7 @@
         <v>76</v>
       </c>
       <c r="E71" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" s="1">
         <v>8</v>
@@ -12458,7 +12410,7 @@
         <v>148</v>
       </c>
       <c r="E72" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2">
         <v>16</v>
@@ -12494,7 +12446,7 @@
         <v>76</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73">
         <v>8</v>
@@ -12530,7 +12482,7 @@
         <v>76</v>
       </c>
       <c r="E74" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74" s="1">
         <v>8</v>
@@ -12566,7 +12518,7 @@
         <v>140</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F75">
         <v>10</v>
@@ -12602,7 +12554,7 @@
         <v>110</v>
       </c>
       <c r="E76">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F76">
         <v>3</v>
@@ -12638,7 +12590,7 @@
         <v>88</v>
       </c>
       <c r="E77">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -12674,7 +12626,7 @@
         <v>91</v>
       </c>
       <c r="E78" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F78" s="1">
         <v>2</v>
@@ -12710,7 +12662,7 @@
         <v>136</v>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79" s="2">
         <v>16</v>
@@ -12746,7 +12698,7 @@
         <v>76</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F80">
         <v>8</v>
@@ -12782,7 +12734,7 @@
         <v>76</v>
       </c>
       <c r="E81" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" s="1">
         <v>8</v>
@@ -12818,7 +12770,7 @@
         <v>148</v>
       </c>
       <c r="E82" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2">
         <v>16</v>
@@ -12854,7 +12806,7 @@
         <v>76</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F83">
         <v>8</v>
@@ -12890,7 +12842,7 @@
         <v>76</v>
       </c>
       <c r="E84" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F84" s="1">
         <v>8</v>
@@ -12926,7 +12878,7 @@
         <v>140</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F85">
         <v>10</v>
@@ -12962,7 +12914,7 @@
         <v>110</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F86">
         <v>3</v>
@@ -12998,7 +12950,7 @@
         <v>88</v>
       </c>
       <c r="E87">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -13034,7 +12986,7 @@
         <v>91</v>
       </c>
       <c r="E88" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>2</v>
@@ -13070,7 +13022,7 @@
         <v>136</v>
       </c>
       <c r="E89" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2">
         <v>16</v>
@@ -13106,7 +13058,7 @@
         <v>76</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90">
         <v>8</v>
@@ -13142,7 +13094,7 @@
         <v>76</v>
       </c>
       <c r="E91" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F91" s="1">
         <v>8</v>
@@ -13178,7 +13130,7 @@
         <v>148</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
@@ -13214,7 +13166,7 @@
         <v>76</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93">
         <v>8</v>
@@ -13250,7 +13202,7 @@
         <v>76</v>
       </c>
       <c r="E94" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F94" s="1">
         <v>8</v>
@@ -13286,7 +13238,7 @@
         <v>246</v>
       </c>
       <c r="E95" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1">
         <v>16</v>
@@ -13322,7 +13274,7 @@
         <v>246</v>
       </c>
       <c r="E96" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2">
         <v>16</v>
@@ -13358,7 +13310,7 @@
         <v>246</v>
       </c>
       <c r="E97" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2">
         <v>16</v>
@@ -13394,7 +13346,7 @@
         <v>246</v>
       </c>
       <c r="E98" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2">
         <v>16</v>
@@ -13430,7 +13382,7 @@
         <v>246</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F99" s="2">
         <v>16</v>
@@ -13466,7 +13418,7 @@
         <v>246</v>
       </c>
       <c r="E100" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1">
         <v>16</v>
@@ -13502,7 +13454,7 @@
         <v>246</v>
       </c>
       <c r="E101" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2">
         <v>16</v>
@@ -13538,7 +13490,7 @@
         <v>246</v>
       </c>
       <c r="E102" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
@@ -13574,7 +13526,7 @@
         <v>246</v>
       </c>
       <c r="E103" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2">
         <v>16</v>
@@ -13610,7 +13562,7 @@
         <v>246</v>
       </c>
       <c r="E104" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F104" s="2">
         <v>16</v>
@@ -13646,7 +13598,7 @@
         <v>246</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2">
         <v>16</v>
@@ -13682,7 +13634,7 @@
         <v>246</v>
       </c>
       <c r="E106" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F106" s="2">
         <v>16</v>
@@ -13718,7 +13670,7 @@
         <v>246</v>
       </c>
       <c r="E107" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2">
         <v>16</v>
@@ -13754,7 +13706,7 @@
         <v>246</v>
       </c>
       <c r="E108" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2">
         <v>16</v>
@@ -13790,7 +13742,7 @@
         <v>246</v>
       </c>
       <c r="E109" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2">
         <v>16</v>
@@ -13826,7 +13778,7 @@
         <v>246</v>
       </c>
       <c r="E110" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F110" s="2">
         <v>16</v>
@@ -13862,7 +13814,7 @@
         <v>246</v>
       </c>
       <c r="E111" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F111" s="2">
         <v>16</v>
@@ -13898,7 +13850,7 @@
         <v>246</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2">
         <v>16</v>
@@ -13934,7 +13886,7 @@
         <v>246</v>
       </c>
       <c r="E113" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2">
         <v>16</v>
@@ -13970,7 +13922,7 @@
         <v>246</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F114" s="2">
         <v>16</v>
@@ -14006,7 +13958,7 @@
         <v>246</v>
       </c>
       <c r="E115" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1">
         <v>16</v>
@@ -14042,7 +13994,7 @@
         <v>246</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2">
         <v>16</v>
@@ -14078,7 +14030,7 @@
         <v>246</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2">
         <v>16</v>
@@ -14114,7 +14066,7 @@
         <v>246</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2">
         <v>16</v>
@@ -14150,7 +14102,7 @@
         <v>246</v>
       </c>
       <c r="E119" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F119" s="2">
         <v>16</v>
@@ -14186,7 +14138,7 @@
         <v>246</v>
       </c>
       <c r="E120" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F120" s="2">
         <v>16</v>
@@ -14222,7 +14174,7 @@
         <v>246</v>
       </c>
       <c r="E121" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F121" s="2">
         <v>16</v>
@@ -14258,7 +14210,7 @@
         <v>246</v>
       </c>
       <c r="E122" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F122" s="2">
         <v>16</v>
@@ -14294,7 +14246,7 @@
         <v>246</v>
       </c>
       <c r="E123" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F123" s="2">
         <v>16</v>
@@ -14330,7 +14282,7 @@
         <v>246</v>
       </c>
       <c r="E124" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F124" s="2">
         <v>16</v>
@@ -14366,7 +14318,7 @@
         <v>246</v>
       </c>
       <c r="E125" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F125" s="2">
         <v>16</v>
@@ -14402,7 +14354,7 @@
         <v>246</v>
       </c>
       <c r="E126" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F126" s="2">
         <v>16</v>
@@ -14438,7 +14390,7 @@
         <v>246</v>
       </c>
       <c r="E127" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F127" s="2">
         <v>16</v>
@@ -14474,7 +14426,7 @@
         <v>136</v>
       </c>
       <c r="E128" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F128" s="2">
         <v>16</v>
@@ -14510,7 +14462,7 @@
         <v>246</v>
       </c>
       <c r="E129" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F129" s="2">
         <v>16</v>
@@ -14535,23 +14487,23 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I2 I130:I999">
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I129">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="notEqual">
+      <formula>E3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J129">
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L129">
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I129">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14601,9 +14553,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -14619,7 +14569,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -14654,7 +14604,7 @@
         <v>281</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -14690,7 +14640,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -14714,17 +14664,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I111">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J111">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L111">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
       <formula>F2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14775,9 +14725,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -14793,7 +14741,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -14828,7 +14776,7 @@
         <v>79</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -14864,7 +14812,7 @@
         <v>80</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -14900,7 +14848,7 @@
         <v>88</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -14936,7 +14884,7 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -14972,7 +14920,7 @@
         <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -15008,7 +14956,7 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -15044,7 +14992,7 @@
         <v>88</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -15080,7 +15028,7 @@
         <v>89</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -15116,7 +15064,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -15152,7 +15100,7 @@
         <v>88</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -15188,7 +15136,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -15224,7 +15172,7 @@
         <v>88</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -15260,7 +15208,7 @@
         <v>88</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -15296,7 +15244,7 @@
         <v>88</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -15332,7 +15280,7 @@
         <v>88</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -15368,7 +15316,7 @@
         <v>88</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -15404,7 +15352,7 @@
         <v>88</v>
       </c>
       <c r="E19" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -15440,7 +15388,7 @@
         <v>91</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -15476,7 +15424,7 @@
         <v>88</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -15512,7 +15460,7 @@
         <v>88</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -15548,7 +15496,7 @@
         <v>88</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -15584,7 +15532,7 @@
         <v>89</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -15620,7 +15568,7 @@
         <v>90</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -15656,7 +15604,7 @@
         <v>110</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -15692,7 +15640,7 @@
         <v>89</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -15728,7 +15676,7 @@
         <v>91</v>
       </c>
       <c r="E28">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -15764,7 +15712,7 @@
         <v>88</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -15800,7 +15748,7 @@
         <v>88</v>
       </c>
       <c r="E30" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
@@ -15836,7 +15784,7 @@
         <v>89</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -15872,7 +15820,7 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -15908,7 +15856,7 @@
         <v>89</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -15944,7 +15892,7 @@
         <v>89</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -15980,7 +15928,7 @@
         <v>89</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -16016,7 +15964,7 @@
         <v>89</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -16052,7 +16000,7 @@
         <v>89</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -16088,7 +16036,7 @@
         <v>89</v>
       </c>
       <c r="E38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -16124,7 +16072,7 @@
         <v>110</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -16160,7 +16108,7 @@
         <v>114</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -16196,7 +16144,7 @@
         <v>116</v>
       </c>
       <c r="E41" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F41" s="1">
         <v>2</v>
@@ -16232,7 +16180,7 @@
         <v>88</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -16268,7 +16216,7 @@
         <v>110</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -16304,7 +16252,7 @@
         <v>88</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -16340,7 +16288,7 @@
         <v>110</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F45">
         <v>3</v>
@@ -16376,7 +16324,7 @@
         <v>88</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -16412,7 +16360,7 @@
         <v>110</v>
       </c>
       <c r="E47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -16448,7 +16396,7 @@
         <v>88</v>
       </c>
       <c r="E48">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -16484,7 +16432,7 @@
         <v>110</v>
       </c>
       <c r="E49" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1">
         <v>3</v>
@@ -16520,7 +16468,7 @@
         <v>88</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -16556,7 +16504,7 @@
         <v>110</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F51">
         <v>3</v>
@@ -16592,7 +16540,7 @@
         <v>88</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -16628,7 +16576,7 @@
         <v>110</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F53">
         <v>3</v>
@@ -16664,7 +16612,7 @@
         <v>88</v>
       </c>
       <c r="E54">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -16700,7 +16648,7 @@
         <v>110</v>
       </c>
       <c r="E55">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F55">
         <v>3</v>
@@ -16736,7 +16684,7 @@
         <v>88</v>
       </c>
       <c r="E56">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -16772,7 +16720,7 @@
         <v>110</v>
       </c>
       <c r="E57" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F57" s="1">
         <v>3</v>
@@ -16808,7 +16756,7 @@
         <v>110</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F58">
         <v>3</v>
@@ -16844,7 +16792,7 @@
         <v>132</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F59">
         <v>4</v>
@@ -16880,7 +16828,7 @@
         <v>88</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -16916,7 +16864,7 @@
         <v>88</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -16952,7 +16900,7 @@
         <v>110</v>
       </c>
       <c r="E62">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F62">
         <v>3</v>
@@ -16988,7 +16936,7 @@
         <v>110</v>
       </c>
       <c r="E63">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F63">
         <v>3</v>
@@ -17024,7 +16972,7 @@
         <v>88</v>
       </c>
       <c r="E64" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F64" s="1">
         <v>1</v>
@@ -17060,7 +17008,7 @@
         <v>136</v>
       </c>
       <c r="E65" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2">
         <v>16</v>
@@ -17096,7 +17044,7 @@
         <v>76</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66">
         <v>8</v>
@@ -17132,7 +17080,7 @@
         <v>76</v>
       </c>
       <c r="E67" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1">
         <v>8</v>
@@ -17168,7 +17116,7 @@
         <v>140</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F68">
         <v>10</v>
@@ -17204,7 +17152,7 @@
         <v>110</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F69">
         <v>3</v>
@@ -17240,7 +17188,7 @@
         <v>88</v>
       </c>
       <c r="E70">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -17276,7 +17224,7 @@
         <v>91</v>
       </c>
       <c r="E71" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F71" s="1">
         <v>2</v>
@@ -17312,7 +17260,7 @@
         <v>136</v>
       </c>
       <c r="E72" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2">
         <v>16</v>
@@ -17348,7 +17296,7 @@
         <v>76</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73">
         <v>8</v>
@@ -17384,7 +17332,7 @@
         <v>76</v>
       </c>
       <c r="E74" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74" s="1">
         <v>8</v>
@@ -17420,7 +17368,7 @@
         <v>148</v>
       </c>
       <c r="E75" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F75" s="2">
         <v>16</v>
@@ -17456,7 +17404,7 @@
         <v>76</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76">
         <v>8</v>
@@ -17492,7 +17440,7 @@
         <v>76</v>
       </c>
       <c r="E77" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" s="1">
         <v>8</v>
@@ -17528,7 +17476,7 @@
         <v>140</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F78">
         <v>10</v>
@@ -17564,7 +17512,7 @@
         <v>110</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F79">
         <v>3</v>
@@ -17600,7 +17548,7 @@
         <v>88</v>
       </c>
       <c r="E80">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -17636,7 +17584,7 @@
         <v>91</v>
       </c>
       <c r="E81" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F81" s="1">
         <v>2</v>
@@ -17672,7 +17620,7 @@
         <v>136</v>
       </c>
       <c r="E82" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2">
         <v>16</v>
@@ -17708,7 +17656,7 @@
         <v>76</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F83">
         <v>8</v>
@@ -17744,7 +17692,7 @@
         <v>76</v>
       </c>
       <c r="E84" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F84" s="1">
         <v>8</v>
@@ -17780,7 +17728,7 @@
         <v>148</v>
       </c>
       <c r="E85" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2">
         <v>16</v>
@@ -17816,7 +17764,7 @@
         <v>76</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86">
         <v>8</v>
@@ -17852,7 +17800,7 @@
         <v>76</v>
       </c>
       <c r="E87" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" s="1">
         <v>8</v>
@@ -17888,7 +17836,7 @@
         <v>140</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F88">
         <v>10</v>
@@ -17924,7 +17872,7 @@
         <v>110</v>
       </c>
       <c r="E89">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -17960,7 +17908,7 @@
         <v>88</v>
       </c>
       <c r="E90">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -17996,7 +17944,7 @@
         <v>91</v>
       </c>
       <c r="E91" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F91" s="1">
         <v>2</v>
@@ -18032,7 +17980,7 @@
         <v>136</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
@@ -18068,7 +18016,7 @@
         <v>76</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93">
         <v>8</v>
@@ -18104,7 +18052,7 @@
         <v>76</v>
       </c>
       <c r="E94" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F94" s="1">
         <v>8</v>
@@ -18140,7 +18088,7 @@
         <v>148</v>
       </c>
       <c r="E95" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2">
         <v>16</v>
@@ -18176,7 +18124,7 @@
         <v>76</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96">
         <v>8</v>
@@ -18212,7 +18160,7 @@
         <v>76</v>
       </c>
       <c r="E97" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F97" s="1">
         <v>8</v>
@@ -18248,7 +18196,7 @@
         <v>140</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F98">
         <v>10</v>
@@ -18284,7 +18232,7 @@
         <v>110</v>
       </c>
       <c r="E99">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F99">
         <v>3</v>
@@ -18320,7 +18268,7 @@
         <v>88</v>
       </c>
       <c r="E100">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -18356,7 +18304,7 @@
         <v>91</v>
       </c>
       <c r="E101" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F101" s="1">
         <v>2</v>
@@ -18392,7 +18340,7 @@
         <v>136</v>
       </c>
       <c r="E102" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
@@ -18428,7 +18376,7 @@
         <v>76</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F103">
         <v>8</v>
@@ -18464,7 +18412,7 @@
         <v>76</v>
       </c>
       <c r="E104" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F104" s="1">
         <v>8</v>
@@ -18500,7 +18448,7 @@
         <v>148</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2">
         <v>16</v>
@@ -18536,7 +18484,7 @@
         <v>76</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F106">
         <v>8</v>
@@ -18572,7 +18520,7 @@
         <v>76</v>
       </c>
       <c r="E107" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F107" s="1">
         <v>8</v>
@@ -18608,7 +18556,7 @@
         <v>140</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F108">
         <v>10</v>
@@ -18644,7 +18592,7 @@
         <v>110</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F109">
         <v>3</v>
@@ -18680,7 +18628,7 @@
         <v>88</v>
       </c>
       <c r="E110">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -18716,7 +18664,7 @@
         <v>91</v>
       </c>
       <c r="E111" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F111" s="1">
         <v>2</v>
@@ -18752,7 +18700,7 @@
         <v>136</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2">
         <v>16</v>
@@ -18788,7 +18736,7 @@
         <v>76</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -18824,7 +18772,7 @@
         <v>76</v>
       </c>
       <c r="E114" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F114" s="1">
         <v>8</v>
@@ -18860,7 +18808,7 @@
         <v>148</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2">
         <v>16</v>
@@ -18896,7 +18844,7 @@
         <v>76</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F116">
         <v>8</v>
@@ -18932,7 +18880,7 @@
         <v>76</v>
       </c>
       <c r="E117" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F117" s="1">
         <v>8</v>
@@ -18968,7 +18916,7 @@
         <v>140</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F118">
         <v>10</v>
@@ -19004,7 +18952,7 @@
         <v>110</v>
       </c>
       <c r="E119">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F119">
         <v>3</v>
@@ -19040,7 +18988,7 @@
         <v>88</v>
       </c>
       <c r="E120">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -19076,7 +19024,7 @@
         <v>91</v>
       </c>
       <c r="E121" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F121" s="1">
         <v>2</v>
@@ -19112,7 +19060,7 @@
         <v>136</v>
       </c>
       <c r="E122" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F122" s="2">
         <v>16</v>
@@ -19148,7 +19096,7 @@
         <v>76</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F123">
         <v>8</v>
@@ -19184,7 +19132,7 @@
         <v>76</v>
       </c>
       <c r="E124" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F124" s="1">
         <v>8</v>
@@ -19220,7 +19168,7 @@
         <v>148</v>
       </c>
       <c r="E125" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F125" s="2">
         <v>16</v>
@@ -19256,7 +19204,7 @@
         <v>76</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F126">
         <v>8</v>
@@ -19292,7 +19240,7 @@
         <v>76</v>
       </c>
       <c r="E127" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F127" s="1">
         <v>8</v>
@@ -19328,7 +19276,7 @@
         <v>140</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F128">
         <v>10</v>
@@ -19364,7 +19312,7 @@
         <v>110</v>
       </c>
       <c r="E129">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F129">
         <v>3</v>
@@ -19400,7 +19348,7 @@
         <v>88</v>
       </c>
       <c r="E130">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -19436,7 +19384,7 @@
         <v>91</v>
       </c>
       <c r="E131" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F131" s="1">
         <v>2</v>
@@ -19472,7 +19420,7 @@
         <v>136</v>
       </c>
       <c r="E132" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F132" s="2">
         <v>16</v>
@@ -19508,7 +19456,7 @@
         <v>76</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F133">
         <v>8</v>
@@ -19544,7 +19492,7 @@
         <v>76</v>
       </c>
       <c r="E134" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F134" s="1">
         <v>8</v>
@@ -19580,7 +19528,7 @@
         <v>148</v>
       </c>
       <c r="E135" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F135" s="2">
         <v>16</v>
@@ -19616,7 +19564,7 @@
         <v>76</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F136">
         <v>8</v>
@@ -19652,7 +19600,7 @@
         <v>76</v>
       </c>
       <c r="E137" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F137" s="1">
         <v>8</v>
@@ -19688,7 +19636,7 @@
         <v>140</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F138">
         <v>10</v>
@@ -19724,7 +19672,7 @@
         <v>110</v>
       </c>
       <c r="E139">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F139">
         <v>3</v>
@@ -19760,7 +19708,7 @@
         <v>88</v>
       </c>
       <c r="E140">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -19796,7 +19744,7 @@
         <v>91</v>
       </c>
       <c r="E141" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F141" s="1">
         <v>2</v>
@@ -19832,7 +19780,7 @@
         <v>136</v>
       </c>
       <c r="E142" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F142" s="2">
         <v>16</v>
@@ -19868,7 +19816,7 @@
         <v>76</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F143">
         <v>8</v>
@@ -19904,7 +19852,7 @@
         <v>76</v>
       </c>
       <c r="E144" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F144" s="1">
         <v>8</v>
@@ -19940,7 +19888,7 @@
         <v>148</v>
       </c>
       <c r="E145" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F145" s="2">
         <v>16</v>
@@ -19976,7 +19924,7 @@
         <v>76</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F146">
         <v>8</v>
@@ -20012,7 +19960,7 @@
         <v>76</v>
       </c>
       <c r="E147" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F147" s="1">
         <v>8</v>
@@ -20048,7 +19996,7 @@
         <v>246</v>
       </c>
       <c r="E148" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F148" s="2">
         <v>16</v>
@@ -20084,7 +20032,7 @@
         <v>246</v>
       </c>
       <c r="E149" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F149" s="2">
         <v>16</v>
@@ -20120,7 +20068,7 @@
         <v>246</v>
       </c>
       <c r="E150" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F150" s="2">
         <v>16</v>
@@ -20156,7 +20104,7 @@
         <v>246</v>
       </c>
       <c r="E151" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F151" s="2">
         <v>16</v>
@@ -20192,7 +20140,7 @@
         <v>246</v>
       </c>
       <c r="E152" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F152" s="2">
         <v>16</v>
@@ -20228,7 +20176,7 @@
         <v>246</v>
       </c>
       <c r="E153" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F153" s="2">
         <v>16</v>
@@ -20264,7 +20212,7 @@
         <v>246</v>
       </c>
       <c r="E154" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F154" s="2">
         <v>16</v>
@@ -20300,7 +20248,7 @@
         <v>246</v>
       </c>
       <c r="E155" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F155" s="2">
         <v>16</v>
@@ -20336,7 +20284,7 @@
         <v>246</v>
       </c>
       <c r="E156" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F156" s="2">
         <v>16</v>
@@ -20372,7 +20320,7 @@
         <v>246</v>
       </c>
       <c r="E157" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F157" s="2">
         <v>16</v>
@@ -20408,7 +20356,7 @@
         <v>246</v>
       </c>
       <c r="E158" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F158" s="2">
         <v>16</v>
@@ -20444,7 +20392,7 @@
         <v>246</v>
       </c>
       <c r="E159" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F159" s="2">
         <v>16</v>
@@ -20480,7 +20428,7 @@
         <v>246</v>
       </c>
       <c r="E160" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F160" s="2">
         <v>16</v>
@@ -20516,7 +20464,7 @@
         <v>136</v>
       </c>
       <c r="E161" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F161" s="2">
         <v>16</v>
@@ -20552,7 +20500,7 @@
         <v>246</v>
       </c>
       <c r="E162" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F162" s="2">
         <v>16</v>
@@ -20576,27 +20524,22 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="notEqual">
+  <conditionalFormatting sqref="C2:C162">
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I162">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J162">
-    <cfRule type="cellIs" dxfId="21" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L162">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C162">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I162">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20646,9 +20589,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -20664,7 +20605,7 @@
         <v>256</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -20699,7 +20640,7 @@
         <v>77</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -20735,7 +20676,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -20758,24 +20699,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2 I5:I111">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="I2:I111">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J111">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L111">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20825,9 +20761,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -20843,7 +20777,7 @@
         <v>256</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -20878,7 +20812,7 @@
         <v>256</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -20914,7 +20848,7 @@
         <v>80</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -20950,7 +20884,7 @@
         <v>88</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -20986,7 +20920,7 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -21022,7 +20956,7 @@
         <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -21058,7 +20992,7 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -21094,7 +21028,7 @@
         <v>88</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -21130,7 +21064,7 @@
         <v>89</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -21166,7 +21100,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -21202,7 +21136,7 @@
         <v>257</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -21238,7 +21172,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -21274,7 +21208,7 @@
         <v>88</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -21310,7 +21244,7 @@
         <v>88</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -21346,7 +21280,7 @@
         <v>88</v>
       </c>
       <c r="E16" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -21382,7 +21316,7 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F17">
         <v>2</v>
@@ -21418,7 +21352,7 @@
         <v>88</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -21454,7 +21388,7 @@
         <v>88</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -21490,7 +21424,7 @@
         <v>88</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -21526,7 +21460,7 @@
         <v>89</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -21562,7 +21496,7 @@
         <v>90</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -21598,7 +21532,7 @@
         <v>110</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -21634,7 +21568,7 @@
         <v>89</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -21670,7 +21604,7 @@
         <v>91</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -21706,7 +21640,7 @@
         <v>88</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -21742,7 +21676,7 @@
         <v>88</v>
       </c>
       <c r="E27" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
@@ -21778,7 +21712,7 @@
         <v>264</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -21814,7 +21748,7 @@
         <v>89</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -21850,7 +21784,7 @@
         <v>89</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -21886,7 +21820,7 @@
         <v>89</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -21922,7 +21856,7 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -21958,7 +21892,7 @@
         <v>89</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -21994,7 +21928,7 @@
         <v>91</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -22030,7 +21964,7 @@
         <v>114</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -22066,7 +22000,7 @@
         <v>116</v>
       </c>
       <c r="E36" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1">
         <v>2</v>
@@ -22102,7 +22036,7 @@
         <v>88</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -22138,7 +22072,7 @@
         <v>110</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -22174,7 +22108,7 @@
         <v>88</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -22210,7 +22144,7 @@
         <v>110</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -22246,7 +22180,7 @@
         <v>88</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -22282,7 +22216,7 @@
         <v>110</v>
       </c>
       <c r="E42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -22318,7 +22252,7 @@
         <v>88</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -22354,7 +22288,7 @@
         <v>110</v>
       </c>
       <c r="E44" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F44" s="1">
         <v>3</v>
@@ -22390,7 +22324,7 @@
         <v>246</v>
       </c>
       <c r="E45" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F45" s="2">
         <v>16</v>
@@ -22426,7 +22360,7 @@
         <v>110</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F46">
         <v>3</v>
@@ -22462,7 +22396,7 @@
         <v>132</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F47">
         <v>4</v>
@@ -22498,7 +22432,7 @@
         <v>88</v>
       </c>
       <c r="E48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -22534,7 +22468,7 @@
         <v>76</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49">
         <v>8</v>
@@ -22570,7 +22504,7 @@
         <v>136</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F50" s="2">
         <v>16</v>
@@ -22606,7 +22540,7 @@
         <v>136</v>
       </c>
       <c r="E51" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1">
         <v>16</v>
@@ -22642,7 +22576,7 @@
         <v>267</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F52">
         <v>14</v>
@@ -22678,7 +22612,7 @@
         <v>91</v>
       </c>
       <c r="E53" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -22714,7 +22648,7 @@
         <v>136</v>
       </c>
       <c r="E54" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F54" s="2">
         <v>16</v>
@@ -22750,7 +22684,7 @@
         <v>76</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F55">
         <v>8</v>
@@ -22786,7 +22720,7 @@
         <v>76</v>
       </c>
       <c r="E56" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" s="1">
         <v>8</v>
@@ -22822,7 +22756,7 @@
         <v>148</v>
       </c>
       <c r="E57" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F57" s="2">
         <v>16</v>
@@ -22858,7 +22792,7 @@
         <v>76</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F58">
         <v>8</v>
@@ -22894,7 +22828,7 @@
         <v>76</v>
       </c>
       <c r="E59" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F59" s="1">
         <v>8</v>
@@ -22930,7 +22864,7 @@
         <v>267</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F60">
         <v>14</v>
@@ -22966,7 +22900,7 @@
         <v>91</v>
       </c>
       <c r="E61" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F61" s="1">
         <v>2</v>
@@ -23002,7 +22936,7 @@
         <v>136</v>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F62" s="2">
         <v>16</v>
@@ -23038,7 +22972,7 @@
         <v>76</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F63">
         <v>8</v>
@@ -23074,7 +23008,7 @@
         <v>76</v>
       </c>
       <c r="E64" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" s="1">
         <v>8</v>
@@ -23110,7 +23044,7 @@
         <v>148</v>
       </c>
       <c r="E65" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2">
         <v>16</v>
@@ -23146,7 +23080,7 @@
         <v>76</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F66">
         <v>8</v>
@@ -23182,7 +23116,7 @@
         <v>76</v>
       </c>
       <c r="E67" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1">
         <v>8</v>
@@ -23218,7 +23152,7 @@
         <v>267</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F68">
         <v>14</v>
@@ -23254,7 +23188,7 @@
         <v>91</v>
       </c>
       <c r="E69" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1">
         <v>2</v>
@@ -23290,7 +23224,7 @@
         <v>136</v>
       </c>
       <c r="E70" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F70" s="2">
         <v>16</v>
@@ -23326,7 +23260,7 @@
         <v>76</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F71">
         <v>8</v>
@@ -23362,7 +23296,7 @@
         <v>76</v>
       </c>
       <c r="E72" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" s="1">
         <v>8</v>
@@ -23398,7 +23332,7 @@
         <v>148</v>
       </c>
       <c r="E73" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73" s="2">
         <v>16</v>
@@ -23434,7 +23368,7 @@
         <v>76</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F74">
         <v>8</v>
@@ -23470,7 +23404,7 @@
         <v>76</v>
       </c>
       <c r="E75" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75" s="1">
         <v>8</v>
@@ -23506,7 +23440,7 @@
         <v>267</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76">
         <v>14</v>
@@ -23542,7 +23476,7 @@
         <v>91</v>
       </c>
       <c r="E77" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F77" s="1">
         <v>2</v>
@@ -23578,7 +23512,7 @@
         <v>136</v>
       </c>
       <c r="E78" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F78" s="2">
         <v>16</v>
@@ -23614,7 +23548,7 @@
         <v>76</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79">
         <v>8</v>
@@ -23650,7 +23584,7 @@
         <v>76</v>
       </c>
       <c r="E80" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="1">
         <v>8</v>
@@ -23686,7 +23620,7 @@
         <v>148</v>
       </c>
       <c r="E81" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F81" s="2">
         <v>16</v>
@@ -23722,7 +23656,7 @@
         <v>76</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F82">
         <v>8</v>
@@ -23758,7 +23692,7 @@
         <v>76</v>
       </c>
       <c r="E83" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F83" s="1">
         <v>8</v>
@@ -23794,7 +23728,7 @@
         <v>246</v>
       </c>
       <c r="E84" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1">
         <v>16</v>
@@ -23830,7 +23764,7 @@
         <v>246</v>
       </c>
       <c r="E85" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2">
         <v>16</v>
@@ -23866,7 +23800,7 @@
         <v>246</v>
       </c>
       <c r="E86" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2">
         <v>16</v>
@@ -23902,7 +23836,7 @@
         <v>246</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2">
         <v>16</v>
@@ -23938,7 +23872,7 @@
         <v>246</v>
       </c>
       <c r="E88" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F88" s="2">
         <v>16</v>
@@ -23974,7 +23908,7 @@
         <v>246</v>
       </c>
       <c r="E89" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1">
         <v>16</v>
@@ -24010,7 +23944,7 @@
         <v>246</v>
       </c>
       <c r="E90" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2">
         <v>16</v>
@@ -24046,7 +23980,7 @@
         <v>246</v>
       </c>
       <c r="E91" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91" s="2">
         <v>16</v>
@@ -24082,7 +24016,7 @@
         <v>246</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
@@ -24118,7 +24052,7 @@
         <v>246</v>
       </c>
       <c r="E93" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2">
         <v>16</v>
@@ -24154,7 +24088,7 @@
         <v>246</v>
       </c>
       <c r="E94" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F94" s="2">
         <v>16</v>
@@ -24190,7 +24124,7 @@
         <v>246</v>
       </c>
       <c r="E95" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2">
         <v>16</v>
@@ -24226,7 +24160,7 @@
         <v>246</v>
       </c>
       <c r="E96" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2">
         <v>16</v>
@@ -24262,7 +24196,7 @@
         <v>246</v>
       </c>
       <c r="E97" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2">
         <v>16</v>
@@ -24298,7 +24232,7 @@
         <v>246</v>
       </c>
       <c r="E98" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2">
         <v>16</v>
@@ -24334,7 +24268,7 @@
         <v>246</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F99" s="2">
         <v>16</v>
@@ -24370,7 +24304,7 @@
         <v>246</v>
       </c>
       <c r="E100" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2">
         <v>16</v>
@@ -24406,7 +24340,7 @@
         <v>246</v>
       </c>
       <c r="E101" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2">
         <v>16</v>
@@ -24442,7 +24376,7 @@
         <v>246</v>
       </c>
       <c r="E102" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
@@ -24478,7 +24412,7 @@
         <v>246</v>
       </c>
       <c r="E103" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2">
         <v>16</v>
@@ -24514,7 +24448,7 @@
         <v>246</v>
       </c>
       <c r="E104" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1">
         <v>16</v>
@@ -24550,7 +24484,7 @@
         <v>246</v>
       </c>
       <c r="E105" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2">
         <v>16</v>
@@ -24586,7 +24520,7 @@
         <v>246</v>
       </c>
       <c r="E106" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F106" s="2">
         <v>16</v>
@@ -24622,7 +24556,7 @@
         <v>246</v>
       </c>
       <c r="E107" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2">
         <v>16</v>
@@ -24658,7 +24592,7 @@
         <v>246</v>
       </c>
       <c r="E108" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2">
         <v>16</v>
@@ -24694,7 +24628,7 @@
         <v>246</v>
       </c>
       <c r="E109" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2">
         <v>16</v>
@@ -24730,7 +24664,7 @@
         <v>246</v>
       </c>
       <c r="E110" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F110" s="2">
         <v>16</v>
@@ -24766,7 +24700,7 @@
         <v>246</v>
       </c>
       <c r="E111" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F111" s="2">
         <v>16</v>
@@ -24802,7 +24736,7 @@
         <v>246</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2">
         <v>16</v>
@@ -24838,7 +24772,7 @@
         <v>246</v>
       </c>
       <c r="E113" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2">
         <v>16</v>
@@ -24874,7 +24808,7 @@
         <v>246</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F114" s="2">
         <v>16</v>
@@ -24910,7 +24844,7 @@
         <v>246</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2">
         <v>16</v>
@@ -24946,7 +24880,7 @@
         <v>246</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2">
         <v>16</v>
@@ -24982,7 +24916,7 @@
         <v>136</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2">
         <v>16</v>
@@ -25018,7 +24952,7 @@
         <v>246</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2">
         <v>16</v>
@@ -25041,24 +24975,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2 I119:I988">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="I2:I988">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J118">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L118">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I118">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25108,9 +25037,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -25126,7 +25053,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -25161,7 +25088,7 @@
         <v>280</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -25197,7 +25124,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -25220,24 +25147,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2 I5:I111">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="I2:I111">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J111">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L111">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I4">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25287,9 +25209,7 @@
       <c r="L1" t="s">
         <v>262</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>282</v>
-      </c>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -25305,7 +25225,7 @@
         <v>77</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -25340,7 +25260,7 @@
         <v>253</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -25376,7 +25296,7 @@
         <v>80</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>8</v>
@@ -25412,7 +25332,7 @@
         <v>88</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -25448,7 +25368,7 @@
         <v>88</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -25484,7 +25404,7 @@
         <v>88</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -25520,7 +25440,7 @@
         <v>88</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -25556,7 +25476,7 @@
         <v>89</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -25592,7 +25512,7 @@
         <v>88</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -25628,7 +25548,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -25664,7 +25584,7 @@
         <v>89</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -25700,7 +25620,7 @@
         <v>88</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -25736,7 +25656,7 @@
         <v>110</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -25772,7 +25692,7 @@
         <v>88</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -25808,7 +25728,7 @@
         <v>88</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -25844,7 +25764,7 @@
         <v>88</v>
       </c>
       <c r="E17" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -25880,7 +25800,7 @@
         <v>91</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -25916,7 +25836,7 @@
         <v>88</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -25952,7 +25872,7 @@
         <v>88</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -25988,7 +25908,7 @@
         <v>89</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -26024,7 +25944,7 @@
         <v>88</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -26060,7 +25980,7 @@
         <v>90</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -26096,7 +26016,7 @@
         <v>110</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24">
         <v>3</v>
@@ -26132,7 +26052,7 @@
         <v>89</v>
       </c>
       <c r="E25">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -26168,7 +26088,7 @@
         <v>91</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F26">
         <v>2</v>
@@ -26204,7 +26124,7 @@
         <v>88</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -26240,7 +26160,7 @@
         <v>88</v>
       </c>
       <c r="E28" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
@@ -26276,7 +26196,7 @@
         <v>255</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -26312,7 +26232,7 @@
         <v>89</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -26348,7 +26268,7 @@
         <v>89</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -26384,7 +26304,7 @@
         <v>89</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -26420,7 +26340,7 @@
         <v>91</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>2</v>
@@ -26456,7 +26376,7 @@
         <v>88</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -26492,7 +26412,7 @@
         <v>114</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -26528,7 +26448,7 @@
         <v>116</v>
       </c>
       <c r="E36" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1">
         <v>2</v>
@@ -26564,7 +26484,7 @@
         <v>255</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F37">
         <v>5</v>
@@ -26600,7 +26520,7 @@
         <v>110</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F38">
         <v>3</v>
@@ -26636,7 +26556,7 @@
         <v>88</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -26672,7 +26592,7 @@
         <v>110</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>3</v>
@@ -26708,7 +26628,7 @@
         <v>88</v>
       </c>
       <c r="E41">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -26744,7 +26664,7 @@
         <v>110</v>
       </c>
       <c r="E42" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F42" s="1">
         <v>3</v>
@@ -26780,7 +26700,7 @@
         <v>246</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F43" s="2">
         <v>16</v>
@@ -26816,7 +26736,7 @@
         <v>88</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -26852,7 +26772,7 @@
         <v>88</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -26888,7 +26808,7 @@
         <v>88</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -26924,7 +26844,7 @@
         <v>275</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F47">
         <v>4</v>
@@ -26960,7 +26880,7 @@
         <v>88</v>
       </c>
       <c r="E48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -26996,7 +26916,7 @@
         <v>76</v>
       </c>
       <c r="E49" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" s="1">
         <v>8</v>
@@ -27032,7 +26952,7 @@
         <v>246</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F50" s="2">
         <v>16</v>
@@ -27068,7 +26988,7 @@
         <v>246</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F51" s="2">
         <v>16</v>
@@ -27104,7 +27024,7 @@
         <v>140</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F52">
         <v>10</v>
@@ -27140,7 +27060,7 @@
         <v>264</v>
       </c>
       <c r="E53">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>4</v>
@@ -27176,7 +27096,7 @@
         <v>91</v>
       </c>
       <c r="E54" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F54" s="1">
         <v>2</v>
@@ -27212,7 +27132,7 @@
         <v>136</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F55" s="2">
         <v>16</v>
@@ -27248,7 +27168,7 @@
         <v>76</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F56">
         <v>8</v>
@@ -27284,7 +27204,7 @@
         <v>76</v>
       </c>
       <c r="E57" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F57" s="1">
         <v>8</v>
@@ -27320,7 +27240,7 @@
         <v>148</v>
       </c>
       <c r="E58" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F58" s="2">
         <v>16</v>
@@ -27356,7 +27276,7 @@
         <v>76</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F59">
         <v>8</v>
@@ -27392,7 +27312,7 @@
         <v>76</v>
       </c>
       <c r="E60" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F60" s="1">
         <v>8</v>
@@ -27428,7 +27348,7 @@
         <v>140</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F61">
         <v>10</v>
@@ -27464,7 +27384,7 @@
         <v>264</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F62">
         <v>4</v>
@@ -27500,7 +27420,7 @@
         <v>91</v>
       </c>
       <c r="E63" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -27536,7 +27456,7 @@
         <v>136</v>
       </c>
       <c r="E64" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F64" s="2">
         <v>16</v>
@@ -27572,7 +27492,7 @@
         <v>76</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F65">
         <v>8</v>
@@ -27608,7 +27528,7 @@
         <v>76</v>
       </c>
       <c r="E66" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" s="1">
         <v>8</v>
@@ -27644,7 +27564,7 @@
         <v>148</v>
       </c>
       <c r="E67" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2">
         <v>16</v>
@@ -27680,7 +27600,7 @@
         <v>76</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F68">
         <v>8</v>
@@ -27716,7 +27636,7 @@
         <v>76</v>
       </c>
       <c r="E69" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" s="1">
         <v>8</v>
@@ -27752,7 +27672,7 @@
         <v>140</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F70">
         <v>10</v>
@@ -27788,7 +27708,7 @@
         <v>264</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F71">
         <v>4</v>
@@ -27824,7 +27744,7 @@
         <v>91</v>
       </c>
       <c r="E72" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F72" s="1">
         <v>2</v>
@@ -27860,7 +27780,7 @@
         <v>136</v>
       </c>
       <c r="E73" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F73" s="2">
         <v>16</v>
@@ -27896,7 +27816,7 @@
         <v>76</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F74">
         <v>8</v>
@@ -27932,7 +27852,7 @@
         <v>76</v>
       </c>
       <c r="E75" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75" s="1">
         <v>8</v>
@@ -27968,7 +27888,7 @@
         <v>148</v>
       </c>
       <c r="E76" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F76" s="2">
         <v>16</v>
@@ -28004,7 +27924,7 @@
         <v>76</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F77">
         <v>8</v>
@@ -28040,7 +27960,7 @@
         <v>76</v>
       </c>
       <c r="E78" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F78" s="1">
         <v>8</v>
@@ -28076,7 +27996,7 @@
         <v>246</v>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79" s="2">
         <v>16</v>
@@ -28112,7 +28032,7 @@
         <v>246</v>
       </c>
       <c r="E80" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F80" s="2">
         <v>16</v>
@@ -28148,7 +28068,7 @@
         <v>246</v>
       </c>
       <c r="E81" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F81" s="2">
         <v>16</v>
@@ -28184,7 +28104,7 @@
         <v>246</v>
       </c>
       <c r="E82" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2">
         <v>16</v>
@@ -28220,7 +28140,7 @@
         <v>246</v>
       </c>
       <c r="E83" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F83" s="2">
         <v>16</v>
@@ -28256,7 +28176,7 @@
         <v>246</v>
       </c>
       <c r="E84" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F84" s="2">
         <v>16</v>
@@ -28292,7 +28212,7 @@
         <v>246</v>
       </c>
       <c r="E85" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2">
         <v>16</v>
@@ -28328,7 +28248,7 @@
         <v>246</v>
       </c>
       <c r="E86" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2">
         <v>16</v>
@@ -28364,7 +28284,7 @@
         <v>246</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2">
         <v>16</v>
@@ -28400,7 +28320,7 @@
         <v>246</v>
       </c>
       <c r="E88" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F88" s="2">
         <v>16</v>
@@ -28436,7 +28356,7 @@
         <v>246</v>
       </c>
       <c r="E89" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2">
         <v>16</v>
@@ -28472,7 +28392,7 @@
         <v>246</v>
       </c>
       <c r="E90" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2">
         <v>16</v>
@@ -28508,7 +28428,7 @@
         <v>246</v>
       </c>
       <c r="E91" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91" s="2">
         <v>16</v>
@@ -28544,7 +28464,7 @@
         <v>246</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
@@ -28580,7 +28500,7 @@
         <v>246</v>
       </c>
       <c r="E93" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2">
         <v>16</v>
@@ -28616,7 +28536,7 @@
         <v>246</v>
       </c>
       <c r="E94" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F94" s="2">
         <v>16</v>
@@ -28652,7 +28572,7 @@
         <v>246</v>
       </c>
       <c r="E95" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2">
         <v>16</v>
@@ -28688,7 +28608,7 @@
         <v>246</v>
       </c>
       <c r="E96" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2">
         <v>16</v>
@@ -28724,7 +28644,7 @@
         <v>246</v>
       </c>
       <c r="E97" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2">
         <v>16</v>
@@ -28760,7 +28680,7 @@
         <v>246</v>
       </c>
       <c r="E98" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2">
         <v>16</v>
@@ -28796,7 +28716,7 @@
         <v>246</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F99" s="2">
         <v>16</v>
@@ -28832,7 +28752,7 @@
         <v>246</v>
       </c>
       <c r="E100" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2">
         <v>16</v>
@@ -28868,7 +28788,7 @@
         <v>246</v>
       </c>
       <c r="E101" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2">
         <v>16</v>
@@ -28904,7 +28824,7 @@
         <v>246</v>
       </c>
       <c r="E102" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
@@ -28940,7 +28860,7 @@
         <v>246</v>
       </c>
       <c r="E103" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2">
         <v>16</v>
@@ -28976,7 +28896,7 @@
         <v>264</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F104">
         <v>4</v>
@@ -29012,7 +28932,7 @@
         <v>264</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F105">
         <v>4</v>
@@ -29048,7 +28968,7 @@
         <v>279</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F106">
         <v>7</v>
@@ -29084,7 +29004,7 @@
         <v>88</v>
       </c>
       <c r="E107" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F107" s="1">
         <v>1</v>
@@ -29120,7 +29040,7 @@
         <v>246</v>
       </c>
       <c r="E108" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2">
         <v>16</v>
@@ -29156,7 +29076,7 @@
         <v>246</v>
       </c>
       <c r="E109" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F109" s="2">
         <v>16</v>
@@ -29192,7 +29112,7 @@
         <v>246</v>
       </c>
       <c r="E110" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F110" s="2">
         <v>16</v>
@@ -29228,7 +29148,7 @@
         <v>246</v>
       </c>
       <c r="E111" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F111" s="2">
         <v>16</v>
@@ -29264,7 +29184,7 @@
         <v>246</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F112" s="2">
         <v>16</v>
@@ -29300,7 +29220,7 @@
         <v>246</v>
       </c>
       <c r="E113" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2">
         <v>16</v>
@@ -29336,7 +29256,7 @@
         <v>246</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F114" s="2">
         <v>16</v>
@@ -29372,7 +29292,7 @@
         <v>246</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2">
         <v>16</v>
@@ -29408,7 +29328,7 @@
         <v>246</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2">
         <v>16</v>
@@ -29444,7 +29364,7 @@
         <v>246</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2">
         <v>16</v>
@@ -29480,7 +29400,7 @@
         <v>246</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2">
         <v>16</v>
@@ -29516,7 +29436,7 @@
         <v>246</v>
       </c>
       <c r="E119" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F119" s="2">
         <v>16</v>
@@ -29552,7 +29472,7 @@
         <v>136</v>
       </c>
       <c r="E120" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F120" s="2">
         <v>16</v>
@@ -29576,24 +29496,19 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="I2:I120">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="notEqual">
       <formula>E2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J120">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="notEqual">
       <formula>A2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L120">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
       <formula>F2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I120">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
-      <formula>E3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
